--- a/dataSource.xlsx
+++ b/dataSource.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters-FG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters-SFN" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM List" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Demand" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Initial Stock" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WL CT " sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tooling-Mold" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preventive-Maintenance" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Material-Arrival-ETA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer-Priority" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production plan-Done" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="排产原则-约束条件" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parameters-FG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parameters-SFN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BOM List" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Customer Demand" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Initial Stock" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="WL CT " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tooling-Mold" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Preventive-Maintenance" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Material-Arrival-ETA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Customer-Priority" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Production plan-Done" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="排产原则-约束条件" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1021"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,998 +1825,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
-    <row r="1001"/>
-    <row r="1002"/>
-    <row r="1003"/>
-    <row r="1004"/>
-    <row r="1005"/>
-    <row r="1006"/>
-    <row r="1007"/>
-    <row r="1008"/>
-    <row r="1009"/>
-    <row r="1010"/>
-    <row r="1011"/>
-    <row r="1012"/>
-    <row r="1013"/>
-    <row r="1014"/>
-    <row r="1015"/>
-    <row r="1016"/>
-    <row r="1017"/>
-    <row r="1018"/>
-    <row r="1019"/>
-    <row r="1020"/>
-    <row r="1021"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5588,10 +4596,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>【逻辑公式】工装模具独占硬约束：若 Mold(Task_i) == M...</t>
+          <t>【逻辑公式】工装模具独占硬约束：若 Mold(Task_i) == Mold(Task_j) 且 i ≠ j，则 [Start_Time(i), End_Time(i)] ∩ [Start_Time(j), End_Time(j)] = ∅。
+【业务边界】共用模具/夹具物理唯一，禁止跨设备并发排产，强制时间轴序列化。
+【场景示例】设备Line 1与Line 2共用模具M01。Line 1安排周二08:00-12:00生产，Line 2若需使用M01，排产最早只能从周二12:00（含换模搬运时间）后开始排入。</t>
         </is>
       </c>
     </row>
@@ -5621,10 +4630,11 @@
           <t>业务策略</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>【异常策略】非均衡波峰响应：支持宏观日历跨周期滚动切片与局部日历弹性分...</t>
+          <t>【异常策略】非均衡波峰响应：支持宏观日历跨周期滚动切片与局部日历弹性分裂调度。
+【业务边界】应对月初集中爆单、月末断崖式闲置等“前端拥堵”极端场景。
+【仿真示例】某月前两周需求10000件（极限产能仅7000件），后两周需求仅1000件。系统不采用全月均摊做五休二，而是前两周启动无休连排+跨月预排+缺口延期组合策略。</t>
         </is>
       </c>
     </row>
@@ -5654,10 +4664,11 @@
           <t>业务策略</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>【排产策略】跨期预产与产能平准化：若 Demand_Far &gt; Cap...</t>
+          <t>【排产策略】跨期预产与产能平准化：若 Demand_Far &gt; Capacity_Far 且 Demand_Near &lt; Capacity_Near，则将远期缺口 Gap_Far 前置到近期空闲窗口提前生产。
+【业务边界】通过削峰填谷平准化产能负荷，防范远期交付挤兑与近期机台闲置。
+【场景示例】某月后半月订单严重超载（缺口2000件），而前半月尚有3000件富余产能。系统自动将后半月2000件工单前置至前半月空闲时段提前排产备库，实现跨期平准化。</t>
         </is>
       </c>
     </row>
@@ -5687,10 +4698,11 @@
           <t>业务策略</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>【异常策略】分段日历粒度：Calendar(Line, Period_...</t>
+          <t>【异常策略】分段日历粒度：Calendar(Line, Period_1) ≠ Calendar(Line, Period_2)，支持同月多套日历组合。
+【业务边界】严禁同月一刀切排班，允许前紧后松动态切换。
+【仿真示例】同一产线在4月第1-2周绑定“7天×24小时连续生产日历”；进入第3-4周订单骤减，系统自动切换绑定为“做三休四集中轮休日历”。</t>
         </is>
       </c>
     </row>
@@ -5720,10 +4732,11 @@
           <t>业务策略</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>【异常策略】产能锁定与延期建议：若 极限产能 + 预排 + 加班 仍无...</t>
+          <t>【异常策略】产能锁定与延期建议：若 极限产能 + 预排 + 加班 仍无法满足交期，锁定超额订单并生成《交期调整建议表》。
+【业务边界】不可抗力交付缺口透明化，算法自动给出最佳延期平移建议日期。
+【场景示例】某紧急订单1500件交期为10日，产线全负荷运转至10日仍有500件绝对缺口。系统锁定该500件并出具告警建议：“建议顺延至20日（月末空闲期）交付”。</t>
         </is>
       </c>
     </row>
@@ -5753,10 +4766,11 @@
           <t>软约束</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>【排班规则】阶梯1（极度空闲）：若 Demand_Weekly ≤ 4...</t>
+          <t>【排班规则】阶梯1（极度空闲）：若 Demand_Weekly ≤ 4/7 × Max_Capacity，Work_Days = {周一, 周二, 周三, 周四}，Off_Days = {周五, 周六, 周日}。
+【业务边界】低负荷时集中压缩开机天数，降本节能。
+【仿真示例】周极限产能7000件。当周总需求仅3500件（≤4000件），系统自动激活“做四休三”日历，周一至周四满负荷生产，周五至周日停工休假。</t>
         </is>
       </c>
     </row>
@@ -5786,10 +4800,11 @@
           <t>软约束</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>【排班规则】阶梯2（正常均衡）：若 4/7 × Max_Cap &lt; D...</t>
+          <t>【排班规则】阶梯2（正常均衡）：若 4/7 × Max_Cap &lt; Demand_Weekly ≤ 5/7 × Max_Cap，Work_Days = {周一至周五}，Off_Days = {周六, 周日}。
+【业务边界】标准法定工作制，工时平准化排程。
+【仿真示例】周极限产能7000件。周需求为4800件（在4000与5000之间），系统激活“做五休二”日历，周一至周五平摊生产960件/天，周六周日产线正常双休。</t>
         </is>
       </c>
     </row>
@@ -5819,10 +4834,11 @@
           <t>软约束</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>【排班规则】阶梯3（产能紧张）：若 Demand_Weekly &gt; 5...</t>
+          <t>【排班规则】阶梯3（产能紧张）：若 Demand_Weekly &gt; 5/7 × Max_Cap，Work_Days = {周一至周日}，Work_Calendar = 连续生产/无休。
+【业务边界】订单高企时打破常规周末休息，全量释放极限产能。
+【仿真示例】周极限产能7000件。周需求达6200件（&gt;5000件），系统触发排班升阶，自动取消周六周日休息，排定7天连续开工以保障准时交付。</t>
         </is>
       </c>
     </row>
@@ -5852,10 +4868,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>【逻辑公式】连续跨班不可分割硬约束：Batch ≥ MPQ；若 班次产...</t>
+          <t>【逻辑公式】连续跨班不可分割硬约束：Batch ≥ MPQ；若 班次产能 &lt; MPQ，连续排产不可换线。
+【业务边界】整批生产不可中途中断，单班做不完强制在下一班连续排满MPQ。
+【场景示例】MPQ为1200件，产线单班仅能做800件。系统自动锁定早班800件+中班400件连续作业，中间严禁切换其他产品。</t>
         </is>
       </c>
     </row>
@@ -5885,10 +4902,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>【逻辑公式】装配围栏保护硬约束：若 Schedule_Time(j) ...</t>
+          <t>【逻辑公式】装配围栏保护硬约束：若 Schedule_Time(j) ∈ [Now, Now + Fence_Period]，Auto_Reschedule(j) = 0。
+【业务边界】锁定总装近端已发工单，杜绝系统频繁变动引发线边物料与人员调配混乱。
+【场景示例】成品总装线设定近端12小时时间围栏。已排产上线并配料的工单被强制锁定，系统重排时不得自动插单、挪移或撤销，修改仅限计划员特批手工调整。</t>
         </is>
       </c>
     </row>
@@ -5923,7 +4941,9 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>【逻辑公式】换型成本与跨班继承软约束（权重80%）：Min ∑ [ 0...</t>
+          <t>【逻辑公式】换型成本与跨班继承软约束（权重80%）：Min ∑ [ 0.80 × Setup_Penalty × 𝕀(Setup_Type(t) ≠ Setup_Type(t-1)) ]；优先保持 Shift_Handover_Setup(t) = Shift_Handover_Setup(t-1)。
+【业务边界】在保交付前提下，极小化单班内及跨班换型损耗，避免交接班因打断产生二次换模。
+【场景示例】班次交接时，前班正在生产产品A（模具M1）。接班次优先接续排产A产品，直至该工单或合并批次完成，严禁无故在接班初始强行切换模具M2。</t>
         </is>
       </c>
     </row>
@@ -5958,7 +4978,9 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>【逻辑公式】顺位填补与跨班连续软约束（权重80%）：若 Utiliza...</t>
+          <t>【逻辑公式】顺位填补与跨班连续软约束（权重80%）：若 Utilization(Shift_t) &lt; 95%，Pull_Order = Order_{Next}(t) 且 跨越班次时 Batch_Merged = 1；禁止跨序拣单 Forbidden(Order_{t+k}, k &gt; 1)。
+【业务边界】防凑单碎片化与频繁断线，保持时间轴完整性，拉取订单跨班保持作业连续性。
+【场景示例】白班负荷仅80%，时间轴紧邻的中班订单需生产4小时。系统将该订单顺位提前至白班末尾开始生产并平滑顺延至中班，两班合并为单一连续批次，禁止跳单挑拣后天急件。</t>
         </is>
       </c>
     </row>
@@ -5988,10 +5010,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>【逻辑公式】成品按单交付硬约束：∑ Output = Total_De...</t>
+          <t>【逻辑公式】成品按单交付硬约束：∑ Output = Total_Demand，严格闭环生产。
+【业务边界】杜绝过度推式生产造成成品高库龄积压，匹配总订单即止。
+【场景示例】某料号总采购订单2000件。系统精准排满2000件后即刻关停工单，不再排入任何无订单预测的额外数量。</t>
         </is>
       </c>
     </row>
@@ -6021,10 +5044,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>【逻辑公式】特定首批跟线时间窗硬约束：Schedule_Range ⊆...</t>
+          <t>【逻辑公式】特定首批跟线时间窗硬约束：Schedule_Range ⊆ Defined_Time_Slot。
+【业务边界】需特殊资源（质检跟线、设备调机）配套的批次，严格限制在指定时间段。
+【场景示例】指定某高端总成只能在周二下午13:00-17:00（质保主管在岗）生产，排程引擎在该时段独占产线排产。</t>
         </is>
       </c>
     </row>
@@ -6059,7 +5083,9 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>【逻辑公式】经济批量对齐软约束（权重25%）：Batch_Qty = ...</t>
+          <t>【逻辑公式】经济批量对齐软约束（权重25%）：Batch_Qty = k × MPQ (k ∈ ℕ⁺)。
+【业务边界】尽量按照标准整批/整箱投料，减少散数、零头料管理成本。
+【场景示例】最小包装量MPQ=500件。需求为650件时，算法权衡凑整为1000件或按650件排产，施加0.25权重约束引导批量规范化。</t>
         </is>
       </c>
     </row>
@@ -6089,10 +5115,11 @@
           <t>测试用例</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>【测试验证】极度空闲用例：输入月需求3000件（极限产能10000件）...</t>
+          <t>【测试验证】极度空闲用例：输入月需求3000件（极限产能10000件）。
+【验证准则】①排产日全部落于周一至周四；②周五至周日开机工时为0；③周四24:00库存值精确覆盖周五至周日的所有发货量。
+【输出断言】Assert(Days_Worked == Mon_Thu) &amp;&amp; Assert(Weekend_Stock_Cover == 100%)。</t>
         </is>
       </c>
     </row>
@@ -6122,10 +5149,11 @@
           <t>测试用例</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>【测试验证】局部脉冲用例：全月总负荷65%（整体做五休二），但第2周突...</t>
+          <t>【测试验证】局部脉冲用例：全月总负荷65%（整体做五休二），但第2周突发激增单周负荷130%。
+【验证准则】①系统第1、3、4周保持做五休二；②仅将第2周局部升阶为做六休一或连续排产；③突发需求消除后自动回退至做五休二。
+【输出断言】Assert(Week2_Calendar == Overtime_7Days) &amp;&amp; Assert(Week3_Calendar == Standard_5Days)。</t>
         </is>
       </c>
     </row>
@@ -6155,10 +5183,11 @@
           <t>测试用例</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>【测试验证】前端拥堵用例：输入前15天负荷150%，后15天负荷20%...</t>
+          <t>【测试验证】前端拥堵用例：输入前15天负荷150%，后15天负荷20%。
+【验证准则】①禁止在后15天均摊排产导致前半月断货；②前半月拉满7×24H极限产能；③剩余溢出订单向前倒排或精准触发交期延期告警。
+【输出断言】Assert(H1_Utilization == 100%) &amp;&amp; Assert(Delay_Notice_Generated == True)。</t>
         </is>
       </c>
     </row>
@@ -6188,10 +5217,11 @@
           <t>测试用例</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>【测试验证】绝对超载用例：全月订单需求 &gt; 全月30天7×24H极限理...</t>
+          <t>【测试验证】绝对超载用例：全月订单需求 &gt; 全月30天7×24H极限理论产能。
+【验证准则】①算法终止无效寻优；②直接计算绝对产能差额 Gap = Total_Demand - Max_Month_Cap；③精准输出《产能瓶颈告警及委外/扩产建议清单》。
+【输出断言】Assert(Status == "CAPACITY_OVERLOAD_EXCEPTION") &amp;&amp; Assert(Gap_Qty &gt; 0)。</t>
         </is>
       </c>
     </row>
@@ -6221,10 +5251,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>【逻辑公式】早班交付截单硬约束：Morning_Shift_Outpu...</t>
+          <t>【逻辑公式】早班交付截单硬约束：Morning_Shift_Output + 初始库存 ≥ 当天客户发货总需求。
+【业务边界】成品当日发运以早班生产入库为截止线，早班下班后必须备齐发货量。
+【场景示例】客户周四提货500件。早班初存100件，周四早班装配量必须≥400件并完工入库，杜绝依赖中班或晚班追赶当天发运。</t>
         </is>
       </c>
     </row>
@@ -6254,10 +5285,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>【逻辑公式】物料齐套开工硬约束：Task_Start(i) ≥ Max...</t>
+          <t>【逻辑公式】物料齐套开工硬约束：Task_Start(i) ≥ Max { Material_Available_Time(m) | m ∈ BOM(i) }。
+【业务边界】工单开工必须100%齐套，物料未入库/未检验放行前禁止排入生产。
+【场景示例】某总成工单需关键注塑件与芯片。注塑件预计周三10:00入库，芯片预计周三14:00到货，则总成工单最早排产开工时间自动锁定为周三14:00之后。</t>
         </is>
       </c>
     </row>
@@ -6292,7 +5324,9 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>【逻辑公式】月末安全库存管控软约束（权重20%）：Month_End_...</t>
+          <t>【逻辑公式】月末安全库存管控软约束（权重20%）：Month_End_Stock ≤ 2 × 日均发货需求。
+【业务边界】在月初及月中产能充裕时，平准化调节日产量，月末库存严禁超过2天。
+【场景示例】日发货量100件，月末安全库存限额200件。系统在月末前夕主动削减高库存物料的日投产，确保月末结存不超200件。</t>
         </is>
       </c>
     </row>
@@ -6327,7 +5361,9 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>【逻辑公式】月末库存压降软约束（权重35%）：Month_End_St...</t>
+          <t>【逻辑公式】月末库存压降软约束（权重35%）：Month_End_Stock ≤ Target_Days × 日均需求。
+【业务边界】月底严格限制半成品沉淀，控制库存占用标准天数。
+【场景示例】安全库存上限为3天用量（300件）。月末排产推演若达420件（超库120件），扣除0.35权重罚分，算法自动减少月末最后两天的投产量。</t>
         </is>
       </c>
     </row>
@@ -6357,10 +5393,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>【逻辑公式】需求分级拉单时间窗硬约束：Pull_Window(Orde...</t>
+          <t>【逻辑公式】需求分级拉单时间窗硬约束：Pull_Window(Order_i) ≤ Max_Advance_Days(Order_Type)；其中正式订单 ≤ 30天，高准度预测 ≤ 10天，波动预测 ≤ 3~5天。
+【业务边界】向前合并批次时严格限制提前期上限，规避低准度预测过早投产导致的死库与缺件风险。
+【场景示例】某产品有下月正式订单和下月波动预测。系统合批时允许拉取30天内的正式订单合并生产，但对波动预测严格限制在5天内，杜绝远期不稳定预测提前生产。</t>
         </is>
       </c>
     </row>
@@ -6390,10 +5427,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>【架构规范】产线-日历解耦：Line_Master 与 Calenda...</t>
+          <t>【架构规范】产线-日历解耦：Line_Master 与 Calendar_Template 保持 N:N 弱关联，通过 [Line_ID, Calendar_ID, 生效时段] 动态绑定。
+【业务边界】严禁在算法核心硬编码 weekend_off=True；日历作为外部可配置数据驱动。
+【架构示例】数据库中创建独立日历库（标准双休、做六休一、四班三倒、停线检修）。算法引擎每次调度根据订单负荷动态调用不同日历ID，不修改底层代码。</t>
         </is>
       </c>
     </row>
@@ -6423,10 +5461,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>【逻辑公式】班次利用率区间硬约束：95.0% ≤ Shift_Util...</t>
+          <t>【逻辑公式】班次利用率区间硬约束：95.0% ≤ Shift_Utilization = (实际排产工时 / 班次额定工时) ≤ 105.0%。
+【业务边界】WE34成品装配开班必须维持高效均衡负荷，严禁低于95%低效开机或超过105%过度超载。
+【场景示例】装配线单班额定产能1000件（合规区间950~1050件）。若排产仅800件（利用率80%）或高达1150件（利用率115%），判定违背硬约束无法下发，系统触发合班或平移调整。</t>
         </is>
       </c>
     </row>
@@ -6456,10 +5495,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>【逻辑公式】维保避让中断硬约束：[Task_Start(k), Tas...</t>
+          <t>【逻辑公式】维保避让中断硬约束：[Task_Start(k), Task_End(k)] ∩ PM_Window = ∅；若任务跨越维保期，自动切分工单或整体向后顺延。
+【业务边界】计划性保养(PM)窗口设备产能清零，禁止任何排产任务占用。
+【场景示例】机台周四13:00-15:00安排定检保养(PM)。原定12:00-16:00生产的4小时批次，系统自动切分为12:00-13:00(前半段)+15:00-18:00(后半段)或整体延至15:00后开工。</t>
         </is>
       </c>
     </row>
@@ -6489,10 +5529,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>【逻辑公式】日内紧急响应硬约束：若订单标记为当日加急，允许插入当天白班...</t>
+          <t>【逻辑公式】日内紧急响应硬约束：若订单标记为当日加急，允许插入当天白班(08:00-16:00)，完工时间 T_finish ≤ 发货截单时间。
+【业务边界】特批白班8小时快速流转，豁免提前1天备货规则。
+【场景示例】周一早08:30客户突加200件紧急订单需当日17:00发车。系统强制插入周一白班排程并在15:30完工入库，保障准时出货。</t>
         </is>
       </c>
     </row>
@@ -6522,10 +5563,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>【逻辑公式】Penalty(断线) = ∞；若 min(I_L, I_...</t>
+          <t>【逻辑公式】Penalty(断线) = ∞；若 min(I_L, I_R) &lt; 装配需求，允许 max(I_L, I_R) &gt; 最大库存阈值。
+【业务边界】装配防断线为绝对第一优先，打破库存上限约束。
+【场景示例】装配线需L/R各100件，现有L:20、R:120（最大库存100）。为补足L缺口80件，共模产出80对，导致R库存激增至200，系统判定合法并放行。</t>
         </is>
       </c>
     </row>
@@ -6555,10 +5597,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>【逻辑公式】同步产出约束：Output(L, t) = Output(...</t>
+          <t>【逻辑公式】同步产出约束：Output(L, t) = Output(R, t) = 模具冲压次数(t) × 型腔配比(1:1)。
+【业务边界】注塑/冲压模具联产品物理绑定，禁止单件排产。
+【场景示例】模具一模两穴(1L+1R)，排产400模次自动生成L件400件与R件400件，不可单独安排L件生产400件而R件为0。</t>
         </is>
       </c>
     </row>
@@ -6588,10 +5631,11 @@
           <t>硬约束</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>【逻辑公式】安全前置期硬约束：时刻 t 的可用库存 Stock(t) ...</t>
+          <t>【逻辑公式】安全前置期硬约束：时刻 t 的可用库存 Stock(t) ≥ ∑ (装配计划需求 [t, t+12H])。
+【业务边界】自制件对后道装配的缓冲期不得少于12小时。
+【场景示例】装配线周二08:00-20:00需消耗500件。注塑机必须在周二08:00前完成生产并检验入库，使08:00动态结存≥500件，否则报错触发前置排产。</t>
         </is>
       </c>
     </row>
@@ -6626,7 +5670,9 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>【逻辑公式】切换频次软约束：Count(换模次数 in 12H) ≤ ...</t>
+          <t>【逻辑公式】切换频次软约束：Count(换模次数 in 12H) ≤ 1；若换模次数 &gt; 1，施加权重0.30惩罚。
+【业务边界】常规单班最多跑2副模具；产能极度紧缺时允许通过损失工时换模来保交付。
+【场景示例】机台12H班次内已有模具A和B。若插入急单模具C，产生第2次换模（损耗45分钟），算法扣除30%权重惩罚，权衡产出损失与断线风险后决策。</t>
         </is>
       </c>
     </row>
@@ -6661,7 +5707,9 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>【逻辑公式】库龄与库容软约束（权重60%）：Inventory(t) ...</t>
+          <t>【逻辑公式】库龄与库容软约束（权重60%）：Inventory(t) ≤ ∑_{k=1..5} Daily_Demand(t+k)。
+【业务边界】成品最大库存上限为动态向前覆盖5天需求，抑制过量积压。
+【场景示例】未来第1至第5天客户总需求为2500件。若排产使库存达到3100件（超额600件），触发0.60权重超库惩罚，驱动排产推后或降速。</t>
         </is>
       </c>
     </row>
@@ -6696,7 +5744,9 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>【逻辑公式】软约束惩罚项：Min ∑ [ 0.80 × OverSto...</t>
+          <t>【逻辑公式】软约束惩罚项：Min ∑ [ 0.80 × OverStock_Cost × Max(0, Stock(t) - Max_Limit) ]。
+【业务边界】库存上限控制，在不断线前提下超库需扣减优化目标得分。
+【场景示例】SFIN件设上限1000件。方案A库存1050件（罚分50×0.8=40），方案B库存950件（罚分0），在均不断线下求解器优先选择方案B。</t>
         </is>
       </c>
     </row>
@@ -6731,7 +5781,9 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>【逻辑公式】双边利用率目标（权重90%）：95% ≤ (实际排产工时 ...</t>
+          <t>【逻辑公式】双边利用率目标（权重90%）：95% ≤ (实际排产工时 / 班次额定工时) ≤ 105%。
+【业务边界】避免产线产能浪费或设备过载过劳，保持生产节奏稳定。
+【场景示例】班次标称产能1000件，合规区间[950, 1050]。若排产800件(利用率80%)或1150件(利用率115%)，优化器按0.90权重施加严重偏离惩罚，推动负荷调整。</t>
         </is>
       </c>
     </row>
@@ -6766,7 +5818,9 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>【逻辑公式】提前出货储备（权重90%）：Day(N)完工结余库存 ≥ ...</t>
+          <t>【逻辑公式】提前出货储备（权重90%）：Day(N)完工结余库存 ≥ Day(N+1)客户发货计划总量。
+【业务边界】建立1天成品安全缓冲期，防范当日生产扰动导致交付违约。
+【场景示例】周三客户要货800件。装配线在周二24:00前的生产结余必须≥800件，确保周三早间直接装车发运。</t>
         </is>
       </c>
     </row>
@@ -6781,7 +5835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O990"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8212,969 +7266,6 @@
         <v>400</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9186,7 +7277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11171,940 +9262,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
-    <row r="1000"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12116,7 +9273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK999"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14785,975 +11942,6 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
-    <row r="999"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15765,7 +11953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E998"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17070,952 +13258,6 @@
         <v>97</v>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
-    <row r="160"/>
-    <row r="161"/>
-    <row r="162"/>
-    <row r="163"/>
-    <row r="164"/>
-    <row r="165"/>
-    <row r="166"/>
-    <row r="167"/>
-    <row r="168"/>
-    <row r="169"/>
-    <row r="170"/>
-    <row r="171"/>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
-    <row r="175"/>
-    <row r="176"/>
-    <row r="177"/>
-    <row r="178"/>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
-    <row r="182"/>
-    <row r="183"/>
-    <row r="184"/>
-    <row r="185"/>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
-    <row r="189"/>
-    <row r="190"/>
-    <row r="191"/>
-    <row r="192"/>
-    <row r="193"/>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
-    <row r="198"/>
-    <row r="199"/>
-    <row r="200"/>
-    <row r="201"/>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
-    <row r="205"/>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
-    <row r="209"/>
-    <row r="210"/>
-    <row r="211"/>
-    <row r="212"/>
-    <row r="213"/>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
-    <row r="217"/>
-    <row r="218"/>
-    <row r="219"/>
-    <row r="220"/>
-    <row r="221"/>
-    <row r="222"/>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
-    <row r="229"/>
-    <row r="230"/>
-    <row r="231"/>
-    <row r="232"/>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
-    <row r="236"/>
-    <row r="237"/>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
-    <row r="243"/>
-    <row r="244"/>
-    <row r="245"/>
-    <row r="246"/>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
-    <row r="250"/>
-    <row r="251"/>
-    <row r="252"/>
-    <row r="253"/>
-    <row r="254"/>
-    <row r="255"/>
-    <row r="256"/>
-    <row r="257"/>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
-    <row r="261"/>
-    <row r="262"/>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
-    <row r="266"/>
-    <row r="267"/>
-    <row r="268"/>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
-    <row r="274"/>
-    <row r="275"/>
-    <row r="276"/>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
-    <row r="280"/>
-    <row r="281"/>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284"/>
-    <row r="285"/>
-    <row r="286"/>
-    <row r="287"/>
-    <row r="288"/>
-    <row r="289"/>
-    <row r="290"/>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
-    <row r="294"/>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297"/>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
-    <row r="301"/>
-    <row r="302"/>
-    <row r="303"/>
-    <row r="304"/>
-    <row r="305"/>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
-    <row r="309"/>
-    <row r="310"/>
-    <row r="311"/>
-    <row r="312"/>
-    <row r="313"/>
-    <row r="314"/>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
-    <row r="318"/>
-    <row r="319"/>
-    <row r="320"/>
-    <row r="321"/>
-    <row r="322"/>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
-    <row r="326"/>
-    <row r="327"/>
-    <row r="328"/>
-    <row r="329"/>
-    <row r="330"/>
-    <row r="331"/>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
-    <row r="335"/>
-    <row r="336"/>
-    <row r="337"/>
-    <row r="338"/>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341"/>
-    <row r="342"/>
-    <row r="343"/>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
-    <row r="347"/>
-    <row r="348"/>
-    <row r="349"/>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352"/>
-    <row r="353"/>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356"/>
-    <row r="357"/>
-    <row r="358"/>
-    <row r="359"/>
-    <row r="360"/>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363"/>
-    <row r="364"/>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369"/>
-    <row r="370"/>
-    <row r="371"/>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374"/>
-    <row r="375"/>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378"/>
-    <row r="379"/>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382"/>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
-    <row r="386"/>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389"/>
-    <row r="390"/>
-    <row r="391"/>
-    <row r="392"/>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395"/>
-    <row r="396"/>
-    <row r="397"/>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400"/>
-    <row r="401"/>
-    <row r="402"/>
-    <row r="403"/>
-    <row r="404"/>
-    <row r="405"/>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408"/>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
-    <row r="412"/>
-    <row r="413"/>
-    <row r="414"/>
-    <row r="415"/>
-    <row r="416"/>
-    <row r="417"/>
-    <row r="418"/>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
-    <row r="422"/>
-    <row r="423"/>
-    <row r="424"/>
-    <row r="425"/>
-    <row r="426"/>
-    <row r="427"/>
-    <row r="428"/>
-    <row r="429"/>
-    <row r="430"/>
-    <row r="431"/>
-    <row r="432"/>
-    <row r="433"/>
-    <row r="434"/>
-    <row r="435"/>
-    <row r="436"/>
-    <row r="437"/>
-    <row r="438"/>
-    <row r="439"/>
-    <row r="440"/>
-    <row r="441"/>
-    <row r="442"/>
-    <row r="443"/>
-    <row r="444"/>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
-    <row r="448"/>
-    <row r="449"/>
-    <row r="450"/>
-    <row r="451"/>
-    <row r="452"/>
-    <row r="453"/>
-    <row r="454"/>
-    <row r="455"/>
-    <row r="456"/>
-    <row r="457"/>
-    <row r="458"/>
-    <row r="459"/>
-    <row r="460"/>
-    <row r="461"/>
-    <row r="462"/>
-    <row r="463"/>
-    <row r="464"/>
-    <row r="465"/>
-    <row r="466"/>
-    <row r="467"/>
-    <row r="468"/>
-    <row r="469"/>
-    <row r="470"/>
-    <row r="471"/>
-    <row r="472"/>
-    <row r="473"/>
-    <row r="474"/>
-    <row r="475"/>
-    <row r="476"/>
-    <row r="477"/>
-    <row r="478"/>
-    <row r="479"/>
-    <row r="480"/>
-    <row r="481"/>
-    <row r="482"/>
-    <row r="483"/>
-    <row r="484"/>
-    <row r="485"/>
-    <row r="486"/>
-    <row r="487"/>
-    <row r="488"/>
-    <row r="489"/>
-    <row r="490"/>
-    <row r="491"/>
-    <row r="492"/>
-    <row r="493"/>
-    <row r="494"/>
-    <row r="495"/>
-    <row r="496"/>
-    <row r="497"/>
-    <row r="498"/>
-    <row r="499"/>
-    <row r="500"/>
-    <row r="501"/>
-    <row r="502"/>
-    <row r="503"/>
-    <row r="504"/>
-    <row r="505"/>
-    <row r="506"/>
-    <row r="507"/>
-    <row r="508"/>
-    <row r="509"/>
-    <row r="510"/>
-    <row r="511"/>
-    <row r="512"/>
-    <row r="513"/>
-    <row r="514"/>
-    <row r="515"/>
-    <row r="516"/>
-    <row r="517"/>
-    <row r="518"/>
-    <row r="519"/>
-    <row r="520"/>
-    <row r="521"/>
-    <row r="522"/>
-    <row r="523"/>
-    <row r="524"/>
-    <row r="525"/>
-    <row r="526"/>
-    <row r="527"/>
-    <row r="528"/>
-    <row r="529"/>
-    <row r="530"/>
-    <row r="531"/>
-    <row r="532"/>
-    <row r="533"/>
-    <row r="534"/>
-    <row r="535"/>
-    <row r="536"/>
-    <row r="537"/>
-    <row r="538"/>
-    <row r="539"/>
-    <row r="540"/>
-    <row r="541"/>
-    <row r="542"/>
-    <row r="543"/>
-    <row r="544"/>
-    <row r="545"/>
-    <row r="546"/>
-    <row r="547"/>
-    <row r="548"/>
-    <row r="549"/>
-    <row r="550"/>
-    <row r="551"/>
-    <row r="552"/>
-    <row r="553"/>
-    <row r="554"/>
-    <row r="555"/>
-    <row r="556"/>
-    <row r="557"/>
-    <row r="558"/>
-    <row r="559"/>
-    <row r="560"/>
-    <row r="561"/>
-    <row r="562"/>
-    <row r="563"/>
-    <row r="564"/>
-    <row r="565"/>
-    <row r="566"/>
-    <row r="567"/>
-    <row r="568"/>
-    <row r="569"/>
-    <row r="570"/>
-    <row r="571"/>
-    <row r="572"/>
-    <row r="573"/>
-    <row r="574"/>
-    <row r="575"/>
-    <row r="576"/>
-    <row r="577"/>
-    <row r="578"/>
-    <row r="579"/>
-    <row r="580"/>
-    <row r="581"/>
-    <row r="582"/>
-    <row r="583"/>
-    <row r="584"/>
-    <row r="585"/>
-    <row r="586"/>
-    <row r="587"/>
-    <row r="588"/>
-    <row r="589"/>
-    <row r="590"/>
-    <row r="591"/>
-    <row r="592"/>
-    <row r="593"/>
-    <row r="594"/>
-    <row r="595"/>
-    <row r="596"/>
-    <row r="597"/>
-    <row r="598"/>
-    <row r="599"/>
-    <row r="600"/>
-    <row r="601"/>
-    <row r="602"/>
-    <row r="603"/>
-    <row r="604"/>
-    <row r="605"/>
-    <row r="606"/>
-    <row r="607"/>
-    <row r="608"/>
-    <row r="609"/>
-    <row r="610"/>
-    <row r="611"/>
-    <row r="612"/>
-    <row r="613"/>
-    <row r="614"/>
-    <row r="615"/>
-    <row r="616"/>
-    <row r="617"/>
-    <row r="618"/>
-    <row r="619"/>
-    <row r="620"/>
-    <row r="621"/>
-    <row r="622"/>
-    <row r="623"/>
-    <row r="624"/>
-    <row r="625"/>
-    <row r="626"/>
-    <row r="627"/>
-    <row r="628"/>
-    <row r="629"/>
-    <row r="630"/>
-    <row r="631"/>
-    <row r="632"/>
-    <row r="633"/>
-    <row r="634"/>
-    <row r="635"/>
-    <row r="636"/>
-    <row r="637"/>
-    <row r="638"/>
-    <row r="639"/>
-    <row r="640"/>
-    <row r="641"/>
-    <row r="642"/>
-    <row r="643"/>
-    <row r="644"/>
-    <row r="645"/>
-    <row r="646"/>
-    <row r="647"/>
-    <row r="648"/>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
-    <row r="700"/>
-    <row r="701"/>
-    <row r="702"/>
-    <row r="703"/>
-    <row r="704"/>
-    <row r="705"/>
-    <row r="706"/>
-    <row r="707"/>
-    <row r="708"/>
-    <row r="709"/>
-    <row r="710"/>
-    <row r="711"/>
-    <row r="712"/>
-    <row r="713"/>
-    <row r="714"/>
-    <row r="715"/>
-    <row r="716"/>
-    <row r="717"/>
-    <row r="718"/>
-    <row r="719"/>
-    <row r="720"/>
-    <row r="721"/>
-    <row r="722"/>
-    <row r="723"/>
-    <row r="724"/>
-    <row r="725"/>
-    <row r="726"/>
-    <row r="727"/>
-    <row r="728"/>
-    <row r="729"/>
-    <row r="730"/>
-    <row r="731"/>
-    <row r="732"/>
-    <row r="733"/>
-    <row r="734"/>
-    <row r="735"/>
-    <row r="736"/>
-    <row r="737"/>
-    <row r="738"/>
-    <row r="739"/>
-    <row r="740"/>
-    <row r="741"/>
-    <row r="742"/>
-    <row r="743"/>
-    <row r="744"/>
-    <row r="745"/>
-    <row r="746"/>
-    <row r="747"/>
-    <row r="748"/>
-    <row r="749"/>
-    <row r="750"/>
-    <row r="751"/>
-    <row r="752"/>
-    <row r="753"/>
-    <row r="754"/>
-    <row r="755"/>
-    <row r="756"/>
-    <row r="757"/>
-    <row r="758"/>
-    <row r="759"/>
-    <row r="760"/>
-    <row r="761"/>
-    <row r="762"/>
-    <row r="763"/>
-    <row r="764"/>
-    <row r="765"/>
-    <row r="766"/>
-    <row r="767"/>
-    <row r="768"/>
-    <row r="769"/>
-    <row r="770"/>
-    <row r="771"/>
-    <row r="772"/>
-    <row r="773"/>
-    <row r="774"/>
-    <row r="775"/>
-    <row r="776"/>
-    <row r="777"/>
-    <row r="778"/>
-    <row r="779"/>
-    <row r="780"/>
-    <row r="781"/>
-    <row r="782"/>
-    <row r="783"/>
-    <row r="784"/>
-    <row r="785"/>
-    <row r="786"/>
-    <row r="787"/>
-    <row r="788"/>
-    <row r="789"/>
-    <row r="790"/>
-    <row r="791"/>
-    <row r="792"/>
-    <row r="793"/>
-    <row r="794"/>
-    <row r="795"/>
-    <row r="796"/>
-    <row r="797"/>
-    <row r="798"/>
-    <row r="799"/>
-    <row r="800"/>
-    <row r="801"/>
-    <row r="802"/>
-    <row r="803"/>
-    <row r="804"/>
-    <row r="805"/>
-    <row r="806"/>
-    <row r="807"/>
-    <row r="808"/>
-    <row r="809"/>
-    <row r="810"/>
-    <row r="811"/>
-    <row r="812"/>
-    <row r="813"/>
-    <row r="814"/>
-    <row r="815"/>
-    <row r="816"/>
-    <row r="817"/>
-    <row r="818"/>
-    <row r="819"/>
-    <row r="820"/>
-    <row r="821"/>
-    <row r="822"/>
-    <row r="823"/>
-    <row r="824"/>
-    <row r="825"/>
-    <row r="826"/>
-    <row r="827"/>
-    <row r="828"/>
-    <row r="829"/>
-    <row r="830"/>
-    <row r="831"/>
-    <row r="832"/>
-    <row r="833"/>
-    <row r="834"/>
-    <row r="835"/>
-    <row r="836"/>
-    <row r="837"/>
-    <row r="838"/>
-    <row r="839"/>
-    <row r="840"/>
-    <row r="841"/>
-    <row r="842"/>
-    <row r="843"/>
-    <row r="844"/>
-    <row r="845"/>
-    <row r="846"/>
-    <row r="847"/>
-    <row r="848"/>
-    <row r="849"/>
-    <row r="850"/>
-    <row r="851"/>
-    <row r="852"/>
-    <row r="853"/>
-    <row r="854"/>
-    <row r="855"/>
-    <row r="856"/>
-    <row r="857"/>
-    <row r="858"/>
-    <row r="859"/>
-    <row r="860"/>
-    <row r="861"/>
-    <row r="862"/>
-    <row r="863"/>
-    <row r="864"/>
-    <row r="865"/>
-    <row r="866"/>
-    <row r="867"/>
-    <row r="868"/>
-    <row r="869"/>
-    <row r="870"/>
-    <row r="871"/>
-    <row r="872"/>
-    <row r="873"/>
-    <row r="874"/>
-    <row r="875"/>
-    <row r="876"/>
-    <row r="877"/>
-    <row r="878"/>
-    <row r="879"/>
-    <row r="880"/>
-    <row r="881"/>
-    <row r="882"/>
-    <row r="883"/>
-    <row r="884"/>
-    <row r="885"/>
-    <row r="886"/>
-    <row r="887"/>
-    <row r="888"/>
-    <row r="889"/>
-    <row r="890"/>
-    <row r="891"/>
-    <row r="892"/>
-    <row r="893"/>
-    <row r="894"/>
-    <row r="895"/>
-    <row r="896"/>
-    <row r="897"/>
-    <row r="898"/>
-    <row r="899"/>
-    <row r="900"/>
-    <row r="901"/>
-    <row r="902"/>
-    <row r="903"/>
-    <row r="904"/>
-    <row r="905"/>
-    <row r="906"/>
-    <row r="907"/>
-    <row r="908"/>
-    <row r="909"/>
-    <row r="910"/>
-    <row r="911"/>
-    <row r="912"/>
-    <row r="913"/>
-    <row r="914"/>
-    <row r="915"/>
-    <row r="916"/>
-    <row r="917"/>
-    <row r="918"/>
-    <row r="919"/>
-    <row r="920"/>
-    <row r="921"/>
-    <row r="922"/>
-    <row r="923"/>
-    <row r="924"/>
-    <row r="925"/>
-    <row r="926"/>
-    <row r="927"/>
-    <row r="928"/>
-    <row r="929"/>
-    <row r="930"/>
-    <row r="931"/>
-    <row r="932"/>
-    <row r="933"/>
-    <row r="934"/>
-    <row r="935"/>
-    <row r="936"/>
-    <row r="937"/>
-    <row r="938"/>
-    <row r="939"/>
-    <row r="940"/>
-    <row r="941"/>
-    <row r="942"/>
-    <row r="943"/>
-    <row r="944"/>
-    <row r="945"/>
-    <row r="946"/>
-    <row r="947"/>
-    <row r="948"/>
-    <row r="949"/>
-    <row r="950"/>
-    <row r="951"/>
-    <row r="952"/>
-    <row r="953"/>
-    <row r="954"/>
-    <row r="955"/>
-    <row r="956"/>
-    <row r="957"/>
-    <row r="958"/>
-    <row r="959"/>
-    <row r="960"/>
-    <row r="961"/>
-    <row r="962"/>
-    <row r="963"/>
-    <row r="964"/>
-    <row r="965"/>
-    <row r="966"/>
-    <row r="967"/>
-    <row r="968"/>
-    <row r="969"/>
-    <row r="970"/>
-    <row r="971"/>
-    <row r="972"/>
-    <row r="973"/>
-    <row r="974"/>
-    <row r="975"/>
-    <row r="976"/>
-    <row r="977"/>
-    <row r="978"/>
-    <row r="979"/>
-    <row r="980"/>
-    <row r="981"/>
-    <row r="982"/>
-    <row r="983"/>
-    <row r="984"/>
-    <row r="985"/>
-    <row r="986"/>
-    <row r="987"/>
-    <row r="988"/>
-    <row r="989"/>
-    <row r="990"/>
-    <row r="991"/>
-    <row r="992"/>
-    <row r="993"/>
-    <row r="994"/>
-    <row r="995"/>
-    <row r="996"/>
-    <row r="997"/>
-    <row r="998"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
